--- a/temp_ventas.xlsx
+++ b/temp_ventas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,718 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-03-14 17:03</t>
+          <t>2025-03-06 07:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tablet 10', Smartphone Galaxy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2099.95</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tarjeta</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:53</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Laptop Core i5, Laptop Core i5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2799.96</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>transferencia</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-03-15 13:19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Carlos López</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Laptop Core i5, Smartphone Galaxy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1199.98</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>transferencia</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-03-02 13:29</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Televisor LED 55'</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2399.97</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tarjeta</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-02-18 21:38</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Carlos López</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Refrigeradora No Frost</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2999.97</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>tarjeta</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-03-01 07:46</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Refrigeradora No Frost</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>tarjeta</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-03-09 07:53</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Laptop Core i5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2099.97</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>transferencia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-03-06 19:22</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Laptop Core i5, Laptop Core i5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3499.95</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>transferencia</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-02-27 17:48</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Carlos López</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Smartphone Galaxy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>999.98</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>efectivo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-03-13 12:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Carlos López</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Smartphone Galaxy, Refrigeradora No Frost</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1499.98</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>efectivo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-03-10 23:51</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tablet 10', Smartphone Galaxy, Tablet 10'</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2499.93</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>transferencia</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-02-13 19:34</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>María García</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Laptop Core i5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1399.98</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>efectivo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-03-13 20:52</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Smartphone Galaxy, Televisor LED 55'</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3399.95</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>efectivo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-02-20 19:57</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>María García</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tarjeta</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-02-18 14:21</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Carlos López</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>tarjeta</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-03-07 11:24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Smartphone Galaxy</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>999.98</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>transferencia</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-02-14 03:31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>María García</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tablet 10'</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>599.98</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>efectivo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-02-18 04:21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>María García</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tablet 10'</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>899.97</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>tarjeta</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-02-22 08:10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Smartphone Galaxy</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1499.97</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>transferencia</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-03-09 15:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>María García</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>efectivo</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-03-15 14:05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Desconocido</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Laptop HP</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>899.99</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Smartphone Galaxy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>499.99</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>efectivo</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
